--- a/results_v3_peacks.xlsx
+++ b/results_v3_peacks.xlsx
@@ -2777,7 +2777,7 @@
         <v>109.2962</v>
       </c>
       <c r="J22" t="n">
-        <v>-21.77865219116211</v>
+        <v>178.7073974609375</v>
       </c>
       <c r="K22" s="11" t="inlineStr">
         <is>
@@ -3323,7 +3323,7 @@
         <v>184.2133</v>
       </c>
       <c r="J28" t="n">
-        <v>-425.2304382324219</v>
+        <v>2.217048645019531</v>
       </c>
       <c r="K28" s="11" t="inlineStr">
         <is>
@@ -3692,7 +3692,7 @@
         </is>
       </c>
       <c r="K32" t="n">
-        <v>8.23321533203125</v>
+        <v>-32.26670837402344</v>
       </c>
       <c r="L32" s="11" t="inlineStr">
         <is>
@@ -4238,7 +4238,7 @@
         </is>
       </c>
       <c r="K38" t="n">
-        <v>3.845954895019531</v>
+        <v>3.28302001953125</v>
       </c>
       <c r="L38" s="11" t="inlineStr">
         <is>

--- a/results_v3_peacks.xlsx
+++ b/results_v3_peacks.xlsx
@@ -391,7 +391,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W62"/>
+  <dimension ref="A1:AC62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="18.21875" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -521,6 +521,36 @@
           <t>p_m_74</t>
         </is>
       </c>
+      <c r="X1" t="inlineStr">
+        <is>
+          <t>p_i_75</t>
+        </is>
+      </c>
+      <c r="Y1" t="inlineStr">
+        <is>
+          <t>p_m_75</t>
+        </is>
+      </c>
+      <c r="Z1" t="inlineStr">
+        <is>
+          <t>p_i_65</t>
+        </is>
+      </c>
+      <c r="AA1" t="inlineStr">
+        <is>
+          <t>p_m_65</t>
+        </is>
+      </c>
+      <c r="AB1" t="inlineStr">
+        <is>
+          <t>p_i_84</t>
+        </is>
+      </c>
+      <c r="AC1" t="inlineStr">
+        <is>
+          <t>p_m_84</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
@@ -2777,7 +2807,7 @@
         <v>109.2962</v>
       </c>
       <c r="J22" t="n">
-        <v>178.7073974609375</v>
+        <v>-32.64851379394531</v>
       </c>
       <c r="K22" s="11" t="inlineStr">
         <is>
@@ -2831,6 +2861,15 @@
         <is>
           <t>\</t>
         </is>
+      </c>
+      <c r="X22" t="n">
+        <v>-1.689689636230469</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>1.196540832519531</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>0.5146102905273438</v>
       </c>
     </row>
     <row r="23">
@@ -2923,6 +2962,15 @@
           <t>\</t>
         </is>
       </c>
+      <c r="X23" t="n">
+        <v>-7.69244384765625</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>-6.195632934570312</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>-5.940788269042969</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
@@ -3014,6 +3062,15 @@
           <t>\</t>
         </is>
       </c>
+      <c r="X24" t="n">
+        <v>-2.532264709472656</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>2.07891845703125</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>-2.279945373535156</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
@@ -3105,6 +3162,15 @@
           <t>\</t>
         </is>
       </c>
+      <c r="X25" t="n">
+        <v>-5.264404296875</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>-0.729248046875</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>-4.369544982910156</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
@@ -3196,6 +3262,15 @@
           <t>\</t>
         </is>
       </c>
+      <c r="X26" t="n">
+        <v>-6.318817138671875</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>-5.4866943359375</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>-9.567428588867188</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
@@ -3287,6 +3362,15 @@
           <t>\</t>
         </is>
       </c>
+      <c r="X27" t="n">
+        <v>-4.535484313964844</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>-3.733642578125</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>-3.35345458984375</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
@@ -3378,6 +3462,15 @@
           <t>\</t>
         </is>
       </c>
+      <c r="X28" t="n">
+        <v>-1.625251770019531</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>3.214691162109375</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>-3.061843872070312</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
@@ -3469,6 +3562,15 @@
           <t>\</t>
         </is>
       </c>
+      <c r="X29" t="n">
+        <v>-3.918678283691406</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>-5.670501708984375</v>
+      </c>
+      <c r="AB29" t="n">
+        <v>-4.624229431152344</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
@@ -3560,6 +3662,15 @@
           <t>\</t>
         </is>
       </c>
+      <c r="X30" t="n">
+        <v>-5.443443298339844</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>8.67230224609375</v>
+      </c>
+      <c r="AB30" t="n">
+        <v>-3.627853393554688</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
@@ -3651,6 +3762,15 @@
           <t>\</t>
         </is>
       </c>
+      <c r="X31" t="n">
+        <v>-8.837013244628906</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>-3.917098999023438</v>
+      </c>
+      <c r="AB31" t="n">
+        <v>-8.28009033203125</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
@@ -3692,7 +3812,7 @@
         </is>
       </c>
       <c r="K32" t="n">
-        <v>-32.26670837402344</v>
+        <v>-10.31519317626953</v>
       </c>
       <c r="L32" s="11" t="inlineStr">
         <is>
@@ -3741,6 +3861,15 @@
       </c>
       <c r="W32" t="n">
         <v>-13.60511016845703</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>-10.81743621826172</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>-10.10443115234375</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>-9.042739868164062</v>
       </c>
     </row>
     <row r="33">
@@ -3833,6 +3962,15 @@
       <c r="W33" t="n">
         <v>22.57445526123047</v>
       </c>
+      <c r="Y33" t="n">
+        <v>19.62686157226562</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>19.11537170410156</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>6.671768188476562</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
@@ -3924,6 +4062,15 @@
       <c r="W34" t="n">
         <v>9.971290588378906</v>
       </c>
+      <c r="Y34" t="n">
+        <v>5.44354248046875</v>
+      </c>
+      <c r="AA34" t="n">
+        <v>7.798179626464844</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>7.624893188476562</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
@@ -4015,6 +4162,15 @@
       <c r="W35" t="n">
         <v>-4.723358154296875</v>
       </c>
+      <c r="Y35" t="n">
+        <v>-3.215576171875</v>
+      </c>
+      <c r="AA35" t="n">
+        <v>-11.72685241699219</v>
+      </c>
+      <c r="AC35" t="n">
+        <v>-11.92973327636719</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
@@ -4106,6 +4262,15 @@
       <c r="W36" t="n">
         <v>8.019668579101562</v>
       </c>
+      <c r="Y36" t="n">
+        <v>5.152755737304688</v>
+      </c>
+      <c r="AA36" t="n">
+        <v>-15.1728515625</v>
+      </c>
+      <c r="AC36" t="n">
+        <v>-10.49641418457031</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
@@ -4197,6 +4362,15 @@
       <c r="W37" t="n">
         <v>-10.03141021728516</v>
       </c>
+      <c r="Y37" t="n">
+        <v>-10.26236724853516</v>
+      </c>
+      <c r="AA37" t="n">
+        <v>-6.900489807128906</v>
+      </c>
+      <c r="AC37" t="n">
+        <v>-11.2120361328125</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
@@ -4288,6 +4462,15 @@
       <c r="W38" t="n">
         <v>-9.322616577148438</v>
       </c>
+      <c r="Y38" t="n">
+        <v>2.825836181640625</v>
+      </c>
+      <c r="AA38" t="n">
+        <v>-3.277595520019531</v>
+      </c>
+      <c r="AC38" t="n">
+        <v>-6.1180419921875</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
@@ -4379,6 +4562,15 @@
       <c r="W39" t="n">
         <v>-4.117668151855469</v>
       </c>
+      <c r="Y39" t="n">
+        <v>2.584915161132812</v>
+      </c>
+      <c r="AA39" t="n">
+        <v>-5.052360534667969</v>
+      </c>
+      <c r="AC39" t="n">
+        <v>-4.476318359375</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
@@ -4470,6 +4662,15 @@
       <c r="W40" t="n">
         <v>-6.003280639648438</v>
       </c>
+      <c r="Y40" t="n">
+        <v>-5.207275390625</v>
+      </c>
+      <c r="AA40" t="n">
+        <v>-6.56707763671875</v>
+      </c>
+      <c r="AC40" t="n">
+        <v>-7.472900390625</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
@@ -4560,6 +4761,15 @@
       </c>
       <c r="W41" t="n">
         <v>-5.087577819824219</v>
+      </c>
+      <c r="Y41" t="n">
+        <v>-7.429702758789062</v>
+      </c>
+      <c r="AA41" t="n">
+        <v>-5.5382080078125</v>
+      </c>
+      <c r="AC41" t="n">
+        <v>-9.362411499023438</v>
       </c>
     </row>
     <row r="42" ht="14.25" customHeight="1"/>
